--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484822_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484822_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6293</v>
+        <v>4.5416</v>
       </c>
       <c r="E2" t="n">
-        <v>4.5549</v>
+        <v>4.6524</v>
       </c>
       <c r="F2" t="n">
-        <v>0.07439999999999999</v>
+        <v>-0.1108</v>
       </c>
       <c r="G2" t="n">
         <v>-0.2114</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2562</v>
+        <v>1.1685</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3709</v>
+        <v>0.4683</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8854</v>
+        <v>0.7002</v>
       </c>
       <c r="V2" t="n">
         <v>3.3958</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>D. ANGELES SANCHEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.4279</v>
+        <v>0.1259</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.4801</v>
+        <v>1.6255</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0521</v>
+        <v>-1.4995</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3999</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.655</v>
+        <v>0.7489</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7449</v>
+        <v>-0.6731</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8592</v>
+        <v>1.4568</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2011</v>
+        <v>1.4157</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6581</v>
+        <v>0.0411</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5407</v>
+        <v>-1.381</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4539</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0868</v>
+        <v>-0.7143</v>
       </c>
       <c r="P4" t="n">
-        <v>-2.0757</v>
+        <v>0.9435</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.8305</v>
+        <v>-0.1887</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8894</v>
+        <v>0.3518</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1328</v>
+        <v>0.0555</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7566000000000001</v>
+        <v>0.2963</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-1.2452</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.3018</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. ANGELES SANCHEZ</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.5968</v>
+        <v>-0.3654</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9821</v>
+        <v>-2.2852</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5789</v>
+        <v>1.9199</v>
       </c>
       <c r="G5" t="n">
-        <v>0.07580000000000001</v>
+        <v>1.3999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7489</v>
+        <v>0.655</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6731</v>
+        <v>0.7449</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4568</v>
+        <v>0.8592</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4157</v>
+        <v>0.2011</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0411</v>
+        <v>0.6581</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.381</v>
+        <v>0.5407</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6667999999999999</v>
+        <v>0.4539</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7143</v>
+        <v>0.0868</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3709</v>
+        <v>0.952</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.5879</v>
+        <v>0.3277</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2169</v>
+        <v>0.6243</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.2452</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9015</v>
+        <v>-1.9738</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8075</v>
+        <v>-2.1972</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0941</v>
+        <v>0.2234</v>
       </c>
       <c r="G6" t="n">
         <v>-2.0185</v>
@@ -922,13 +922,13 @@
         <v>2.6418</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7507</v>
+        <v>-0.823</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.511</v>
+        <v>-0.9006999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2398</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>2.1886</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.6496</v>
+        <v>-5.0409</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1931</v>
+        <v>-3.6284</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4565</v>
+        <v>-1.4125</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.4845</v>
+        <v>-0.8266</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.229</v>
+        <v>1.5981</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.2555</v>
+        <v>-2.4247</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.7563</v>
+        <v>0.5133</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1068</v>
+        <v>3.1116</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6496</v>
+        <v>-2.5982</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.7281</v>
+        <v>-1.3399</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1222</v>
+        <v>-1.5135</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6059</v>
+        <v>0.1736</v>
       </c>
       <c r="P7" t="n">
         <v>-1.1322</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.8305</v>
+        <v>-3.774</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6983</v>
+        <v>2.6418</v>
       </c>
       <c r="S7" t="n">
-        <v>5.4575</v>
+        <v>-0.5917</v>
       </c>
       <c r="T7" t="n">
-        <v>5.0354</v>
+        <v>-0.9903</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4221</v>
+        <v>0.3986</v>
       </c>
       <c r="V7" t="n">
         <v>-2.4904</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0.6226</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8488</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.7049</v>
+        <v>-5.1099</v>
       </c>
       <c r="E8" t="n">
-        <v>-4.213</v>
+        <v>-4.8863</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4919</v>
+        <v>-0.2236</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8266</v>
+        <v>-4.9994</v>
       </c>
       <c r="H8" t="n">
-        <v>1.5981</v>
+        <v>-2.9841</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.4247</v>
+        <v>-2.0154</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5133</v>
+        <v>-2.9899</v>
       </c>
       <c r="K8" t="n">
-        <v>3.1116</v>
+        <v>-2.3815</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.5982</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3399</v>
+        <v>-2.0095</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.5135</v>
+        <v>-0.6026</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1736</v>
+        <v>-1.4069</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.774</v>
+        <v>-2.0757</v>
       </c>
       <c r="R8" t="n">
-        <v>2.6418</v>
+        <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2557</v>
+        <v>0.5313</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.5749</v>
+        <v>-0.1225</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3193</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.4904</v>
+        <v>0.3018</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6226</v>
+        <v>0.3018</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.7545</v>
+        <v>-5.6558</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.822</v>
+        <v>-4.2522</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0674</v>
+        <v>-1.4036</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.9994</v>
+        <v>-4.4845</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.9841</v>
+        <v>-3.229</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0154</v>
+        <v>-1.2555</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.9899</v>
+        <v>-2.7563</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.3815</v>
+        <v>-2.1068</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.6496</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0095</v>
+        <v>-1.7281</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6026</v>
+        <v>-1.1222</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.4069</v>
+        <v>-0.6059</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0757</v>
+        <v>-2.8305</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>1.6983</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1134</v>
+        <v>2.4513</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0582</v>
+        <v>1.9763</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9447</v>
+        <v>0.475</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3018</v>
+        <v>-2.4904</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.8488</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.1874</v>
+        <v>-5.8002</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.7609</v>
+        <v>-4.2149</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4265</v>
+        <v>-1.5853</v>
       </c>
       <c r="G10" t="n">
         <v>-4.8552</v>
@@ -1234,13 +1234,13 @@
         <v>3.0192</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6719000000000001</v>
+        <v>-0.2847</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2904</v>
+        <v>-0.7445000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6185</v>
+        <v>0.4598</v>
       </c>
       <c r="V10" t="n">
         <v>-2.5473</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-10.9363</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-8.774900000000001</v>
+        <v>-7.9367</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.1614</v>
+        <v>-1.9233</v>
       </c>
       <c r="G11" t="n">
         <v>-6.6617</v>
@@ -1312,13 +1312,13 @@
         <v>1.887</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.5955</v>
+        <v>-0.5191</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2933</v>
+        <v>-0.4551</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3021</v>
+        <v>-0.064</v>
       </c>
       <c r="V11" t="n">
         <v>-1.547</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-28.8957</v>
+        <v>-28.5046</v>
       </c>
       <c r="E12" t="n">
-        <v>-22.8806</v>
+        <v>-22.4891</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.0154</v>
+        <v>-6.015300000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-21.9477</v>
@@ -1378,7 +1378,7 @@
         <v>-9.437899999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.409400000000001</v>
+        <v>-5.4094</v>
       </c>
       <c r="P12" t="n">
         <v>-4.717500000000001</v>
@@ -1390,13 +1390,13 @@
         <v>16.0395</v>
       </c>
       <c r="S12" t="n">
-        <v>2.844999999999999</v>
+        <v>3.2364</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7765999999999997</v>
+        <v>-0.3853000000000003</v>
       </c>
       <c r="U12" t="n">
-        <v>3.6216</v>
+        <v>3.621599999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-5.0757</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.1176</v>
+        <v>9.7737</v>
       </c>
       <c r="E13" t="n">
         <v>3.5849</v>
       </c>
       <c r="F13" t="n">
-        <v>6.5326</v>
+        <v>6.1887</v>
       </c>
       <c r="G13" t="n">
         <v>4.8806</v>
@@ -1468,13 +1468,13 @@
         <v>3.2079</v>
       </c>
       <c r="S13" t="n">
-        <v>0.331</v>
+        <v>-0.0129</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3252</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6562</v>
+        <v>0.3123</v>
       </c>
       <c r="V13" t="n">
         <v>1.8868</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T. GOODMAN</t>
+          <t>D. SARRIAS SANCHEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.104</v>
+        <v>5.9746</v>
       </c>
       <c r="E14" t="n">
-        <v>3.0061</v>
+        <v>1.4362</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0979</v>
+        <v>4.5384</v>
       </c>
       <c r="G14" t="n">
-        <v>5.7596</v>
+        <v>2.7664</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1556</v>
+        <v>0.08840000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6041</v>
+        <v>2.678</v>
       </c>
       <c r="J14" t="n">
-        <v>5.1019</v>
+        <v>1.5733</v>
       </c>
       <c r="K14" t="n">
-        <v>5.0352</v>
+        <v>0.6926</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0667</v>
+        <v>0.8808</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6578000000000001</v>
+        <v>1.1931</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.8796</v>
+        <v>-0.6041</v>
       </c>
       <c r="O14" t="n">
-        <v>1.5374</v>
+        <v>1.7972</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3209</v>
+        <v>2.0757</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.9627</v>
+        <v>-1.1322</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6418</v>
+        <v>3.2079</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3068</v>
+        <v>-0.7733</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0181</v>
+        <v>-0.8727</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2887</v>
+        <v>0.0994</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6415999999999999</v>
+        <v>1.9058</v>
       </c>
       <c r="W14" t="n">
-        <v>1.8488</v>
+        <v>1.8678</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.4904</v>
+        <v>0.038</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. SARRIAS SANCHEZ</t>
+          <t>T. GOODMAN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.5193</v>
+        <v>4.368</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8516</v>
+        <v>2.6164</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6677</v>
+        <v>1.7516</v>
       </c>
       <c r="G15" t="n">
-        <v>2.7664</v>
+        <v>5.7596</v>
       </c>
       <c r="H15" t="n">
-        <v>0.08840000000000001</v>
+        <v>4.1556</v>
       </c>
       <c r="I15" t="n">
-        <v>2.678</v>
+        <v>1.6041</v>
       </c>
       <c r="J15" t="n">
-        <v>1.5733</v>
+        <v>5.1019</v>
       </c>
       <c r="K15" t="n">
-        <v>0.6926</v>
+        <v>5.0352</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8808</v>
+        <v>0.0667</v>
       </c>
       <c r="M15" t="n">
-        <v>1.1931</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6041</v>
+        <v>-0.8796</v>
       </c>
       <c r="O15" t="n">
-        <v>1.7972</v>
+        <v>1.5374</v>
       </c>
       <c r="P15" t="n">
-        <v>2.0757</v>
+        <v>-1.3209</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1322</v>
+        <v>-3.9627</v>
       </c>
       <c r="R15" t="n">
-        <v>3.2079</v>
+        <v>2.6418</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.2285</v>
+        <v>0.5708</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.4574</v>
+        <v>-0.3716</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7712</v>
+        <v>0.9424</v>
       </c>
       <c r="V15" t="n">
-        <v>1.9058</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>1.8678</v>
+        <v>1.8488</v>
       </c>
       <c r="X15" t="n">
-        <v>0.038</v>
+        <v>-2.4904</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.0453</v>
+        <v>3.6642</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1123</v>
+        <v>2.2097</v>
       </c>
       <c r="F16" t="n">
-        <v>1.933</v>
+        <v>1.4545</v>
       </c>
       <c r="G16" t="n">
         <v>1.216</v>
@@ -1702,13 +1702,13 @@
         <v>1.1322</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0371</v>
+        <v>-0.344</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7055</v>
+        <v>-0.608</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7425</v>
+        <v>0.264</v>
       </c>
       <c r="V16" t="n">
         <v>2.7922</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. RODRIGUEZ GUTIERREZ</t>
+          <t>L. CARRION GALINDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.344</v>
+        <v>2.9889</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5283</v>
+        <v>1.2829</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8157</v>
+        <v>1.7059</v>
       </c>
       <c r="G17" t="n">
-        <v>2.9454</v>
+        <v>1.2317</v>
       </c>
       <c r="H17" t="n">
-        <v>0.774</v>
+        <v>-0.5846</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1714</v>
+        <v>1.8162</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1033</v>
+        <v>1.5803</v>
       </c>
       <c r="K17" t="n">
-        <v>1.231</v>
+        <v>0.1323</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8723</v>
+        <v>1.4481</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8421</v>
+        <v>-0.3487</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.457</v>
+        <v>-0.7168</v>
       </c>
       <c r="O17" t="n">
-        <v>1.2991</v>
+        <v>0.3682</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.1887</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.887</v>
+        <v>-2.0757</v>
       </c>
       <c r="R17" t="n">
-        <v>1.887</v>
+        <v>2.2644</v>
       </c>
       <c r="S17" t="n">
-        <v>1.0023</v>
+        <v>-1.2427</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3121</v>
+        <v>-0.6931</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6902</v>
+        <v>-0.5496</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6036</v>
+        <v>2.8112</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4714</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6036</v>
+        <v>0.3398</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. CARRION GALINDO</t>
+          <t>H. RODRIGUEZ GUTIERREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.7508</v>
+        <v>2.8893</v>
       </c>
       <c r="E18" t="n">
-        <v>1.2829</v>
+        <v>-0.0563</v>
       </c>
       <c r="F18" t="n">
-        <v>1.4678</v>
+        <v>2.9456</v>
       </c>
       <c r="G18" t="n">
-        <v>1.2317</v>
+        <v>2.9454</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.5846</v>
+        <v>0.774</v>
       </c>
       <c r="I18" t="n">
-        <v>1.8162</v>
+        <v>2.1714</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5803</v>
+        <v>2.1033</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1323</v>
+        <v>1.231</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4481</v>
+        <v>0.8723</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3487</v>
+        <v>0.8421</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7168</v>
+        <v>-0.457</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3682</v>
+        <v>1.2991</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0757</v>
+        <v>-1.887</v>
       </c>
       <c r="R18" t="n">
-        <v>2.2644</v>
+        <v>1.887</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4808</v>
+        <v>0.5476</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6931</v>
+        <v>-0.2725</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7877</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>2.8112</v>
+        <v>-0.6036</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4714</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3398</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="19">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0633</v>
+        <v>0.591</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1705</v>
+        <v>-0.7808</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1072</v>
+        <v>1.3718</v>
       </c>
       <c r="G20" t="n">
         <v>2.2676</v>
@@ -2014,13 +2014,13 @@
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7083</v>
+        <v>-0.0541</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5291</v>
+        <v>-0.1394</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1793</v>
+        <v>0.0853</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2452</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.238</v>
+        <v>-0.1587</v>
       </c>
       <c r="E21" t="n">
         <v>-0.8512</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6132</v>
+        <v>0.6926</v>
       </c>
       <c r="G21" t="n">
         <v>0.1996</v>
@@ -2092,13 +2092,13 @@
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0529</v>
+        <v>0.1323</v>
       </c>
       <c r="T21" t="n">
         <v>0.0711</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0182</v>
+        <v>0.0611</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3018</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>E. RHAIEM SANCHEZ</t>
+          <t>T. SASTRE MIR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.596</v>
+        <v>-0.3563</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.2864</v>
+        <v>-2.8102</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.3096</v>
+        <v>2.4539</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0369</v>
+        <v>0.6782</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4069</v>
+        <v>1.4165</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.63</v>
+        <v>-0.7383</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-0.7822</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.1254</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.6084000000000001</v>
+        <v>-1.9076</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4285</v>
+        <v>1.4604</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4069</v>
+        <v>0.2911</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0216</v>
+        <v>1.1692</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9435</v>
+        <v>0.3774</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R22" t="n">
-        <v>0.9435</v>
+        <v>2.2644</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5026</v>
+        <v>-0.1856</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2816</v>
+        <v>-0.141</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.221</v>
+        <v>-0.0446</v>
       </c>
       <c r="V22" t="n">
-        <v>-0</v>
+        <v>-1.2262</v>
       </c>
       <c r="W22" t="n">
-        <v>0.6036</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6036</v>
+        <v>-1.2262</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T. SASTRE MIR</t>
+          <t>D. KEITA DIALLO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.6533</v>
+        <v>-0.7118</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7127</v>
+        <v>-1.5807</v>
       </c>
       <c r="F23" t="n">
-        <v>2.0594</v>
+        <v>0.8689</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6782</v>
+        <v>-0.2113</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4165</v>
+        <v>-0.4711</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7383</v>
+        <v>0.2598</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.7822</v>
+        <v>-0.6496</v>
       </c>
       <c r="K23" t="n">
-        <v>1.1254</v>
+        <v>-0.6496</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.9076</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1.4604</v>
+        <v>0.4383</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2911</v>
+        <v>0.1784</v>
       </c>
       <c r="O23" t="n">
-        <v>1.1692</v>
+        <v>0.2598</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.887</v>
+        <v>-0.9435</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2644</v>
+        <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4826</v>
+        <v>-0.1987</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.0436</v>
+        <v>0.0123</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4391</v>
+        <v>-0.211</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2262</v>
+        <v>-0.3018</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2262</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. KEITA DIALLO</t>
+          <t>E. RHAIEM SANCHEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.6853</v>
+        <v>-0.7282999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.5807</v>
+        <v>-0.2864</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8954</v>
+        <v>-0.4419</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.2113</v>
+        <v>-1.0369</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4711</v>
+        <v>-0.4069</v>
       </c>
       <c r="I24" t="n">
-        <v>0.2598</v>
+        <v>-0.63</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6496</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6496</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4383</v>
+        <v>-0.4285</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1784</v>
+        <v>-0.4069</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2598</v>
+        <v>-0.0216</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>0.9435</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.9435</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0.9435</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1722</v>
+        <v>-0.6349</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0123</v>
+        <v>-0.2816</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1846</v>
+        <v>-0.3533</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.3018</v>
+        <v>-0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.6036</v>
       </c>
       <c r="X24" t="n">
-        <v>-0.3018</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>28.896</v>
+        <v>29.5455</v>
       </c>
       <c r="E25" t="n">
-        <v>6.015499999999999</v>
+        <v>6.0154</v>
       </c>
       <c r="F25" t="n">
-        <v>22.8803</v>
+        <v>23.53</v>
       </c>
       <c r="G25" t="n">
         <v>21.9478</v>
       </c>
       <c r="H25" t="n">
-        <v>6.2529</v>
+        <v>6.252899999999999</v>
       </c>
       <c r="I25" t="n">
         <v>15.6947</v>
@@ -2380,7 +2380,7 @@
         <v>14.8474</v>
       </c>
       <c r="K25" t="n">
-        <v>9.437999999999999</v>
+        <v>9.438000000000002</v>
       </c>
       <c r="L25" t="n">
         <v>5.409599999999999</v>
@@ -2404,13 +2404,13 @@
         <v>20.757</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.8449</v>
+        <v>-2.1955</v>
       </c>
       <c r="T25" t="n">
-        <v>-3.621900000000001</v>
+        <v>-3.6217</v>
       </c>
       <c r="U25" t="n">
-        <v>0.7765000000000001</v>
+        <v>1.4261</v>
       </c>
       <c r="V25" t="n">
         <v>5.075799999999999</v>
@@ -2419,7 +2419,7 @@
         <v>10.829</v>
       </c>
       <c r="X25" t="n">
-        <v>-5.7532</v>
+        <v>-5.753200000000001</v>
       </c>
     </row>
   </sheetData>
